--- a/nvidia_test_suite/latest/model_list.xlsx
+++ b/nvidia_test_suite/latest/model_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17230"/>
   </bookViews>
   <sheets>
     <sheet name="NVIDIA" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="91">
   <si>
     <t>模型名称</t>
   </si>
@@ -44,7 +44,13 @@
     <t>H20 (96G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model deepseek --tokenizer /home/weight/DeepSeek-R1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -ep 8 --attn-dp-size 8 --tokens-per-prediction 2 --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-R1 --tokenizer /home/weight/DeepSeek-R1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --tokens-per-prediction 2 --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
+  </si>
+  <si>
+    <t>DeepSeek-V3.1</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-V3.1 --tokenizer /home/weight/DeepSeek-V3.1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --tokens-per-prediction 2 --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>DeepSeek-R1-0528</t>
@@ -53,46 +59,46 @@
     <t>H20 (96G) 长上下文</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model deepseek --tokenizer /home/weight/DeepSeek-R1-0528/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.99 --prometheus-port 28880 --use-group-gemm -ep 8 --split-embedding --tokens-per-prediction 2 --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-R1-0528 --tokenizer /home/weight/DeepSeek-R1-0528/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.99 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --split-embedding --tokens-per-prediction 2 --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>DeepSeek-V3-0324</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model DeepSeek-V3-0324 --tokenizer /home/weight/DeepSeek-V3-0324 -ep 8 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 4096 --reset-max-seq-len 4096 --gpu-memory-utilization 0.98 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-V3-0324 --tokenizer /home/weight/DeepSeek-V3-0324 -tp 8 -ep 8 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --reset-max-seq-len 4096 --gpu-memory-utilization 0.98 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>Qwen3-235B-A22B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-235B-A22B --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B -ep 8 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-235B-A22B --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B -tp 8 -ep 8 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-235B-A22B-FP8</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-235B-A22B-FP8 --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B-FP8 -ep 4 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-235B-A22B-FP8 --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B-FP8 -tp 4 -ep 4 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-32B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-32B --tokenizer /home/weight/Qwen3/Qwen3-32B -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-32B --tokenizer /home/weight/Qwen3/Qwen3-32B -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-32B-FP8</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-32B-FP8 --tokenizer /home/weight/Qwen3/Qwen/Qwen3-32B-FP8 -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
-  </si>
-  <si>
-    <t>DeepSeek-R1-awq</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-32B-FP8 --tokenizer /home/weight/Qwen3/Qwen3-32B-FP8 -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --split-embedding --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>DeepSeek-R1-AWQ</t>
   </si>
   <si>
     <t>H100 (80G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model deepseek --tokenizer /home/weight/DeepSeek-R1-AWQ/ --tensor-parallel-size 8 --port 2888 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.98 --platform-type nvidia --use-prefix-cache --use-marlin --use-marlin-wna16 --weight-dtype=FP16 --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --rm --privileged --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ --tensor-parallel-size 8 --port 2888 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.98 --platform-type nvidia --use-prefix-cache --use-marlin --use-marlin-wna16 --weight-dtype=FP16 --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-1.5B</t>
@@ -101,19 +107,19 @@
     <t>H100/A100 (80G)、L40s/L20 (48G)、H20 (96G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-1.5B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-1.5B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-1.5B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-1.5B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-7B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-7B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-7B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-7B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-7B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-14B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-14B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-14B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-14B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-14B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-32B</t>
@@ -122,157 +128,178 @@
     <t>H100/A100 (80G)、H20 (96G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>L40s/L20 (48G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Llama-8B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-8B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-8B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-8B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-8B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Llama-70B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Meta-Llama-3.1-8B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-8B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-8B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-8B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-8B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Meta-Llama-3.1-70B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+  </si>
+  <si>
+    <t>Meta-Llama-3.1-70B-Instruct_L-Series</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct_L-Series --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Qwen2.5-0.5B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct --tokenizer /home/weight/Qwen2.5-0.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct --tokenizer /home/weight/Qwen2.5-0.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-1.5B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct --tokenizer /home/weight/Qwen2.5-1.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct --tokenizer /home/weight/Qwen2.5-1.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-3B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct --tokenizer /home/weight/Qwen2.5-3B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct --tokenizer /home/weight/Qwen2.5-3B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-7B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct --tokenizer /home/weight/Qwen2.5-7B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct --tokenizer /home/weight/Qwen2.5-7B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-14B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct --tokenizer /home/weight/Qwen2.5-14B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct --tokenizer /home/weight/Qwen2.5-14B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-32B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>Qwen2.5-32B-Instruct_L-Series</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct_L-Series --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-72B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight -e "CUDA_VISIBLE_DEVICES=4,5,6,7" docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28877 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 4321 --prometheus-port 8007 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>Qwen2.5-72B-Instruct_L-Series</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight -e "CUDA_VISIBLE_DEVICES=4,5,6,7" docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28877 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct_L-Series --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 4321 --prometheus-port 8007 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>QwQ-32B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/QwQ-32B -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/QwQ-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/Qwen/QwQ-32B -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>QwQ-32B_L-Series</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B_L-Series --tokenizer /home/weight/Qwen/QwQ-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-0.5B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-0.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-0.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-1.5B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-1.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-1.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-3B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-3B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-3B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-7B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-7B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-7B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-14B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-14B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-14B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-32B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-32B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-32B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-72B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>Qwen2.5-72B-Instruct-AWQ_L-Series</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ_L-Series --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>QwQ-32B-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B-AWQ --tokenizer /home/weight/QwQ-32B-AWQ -tp 1 --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B-AWQ --tokenizer /home/weight/Qwen/QwQ-32B-AWQ -tp 1 --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-30B-A3B-Instruct-2507</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-30B-A3B-Instruct-2507 --tokenizer /home/weight/qwen/Qwen3-30B-A3B-Instruct-2507 -ep 2 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-30B-A3B-Instruct-2507 --tokenizer /home/weight/qwen/Qwen3-30B-A3B-Instruct-2507 -tp 2 -ep 2 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>Qwen3-32B-AWQ</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen3-32B-AWQ --tokenizer /home/weight/Qwen/Qwen3-32B-AWQ -tp 1 --weight-dtype=FP16 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
 </sst>
 </file>
@@ -301,6 +328,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="宋体"/>
@@ -308,15 +342,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FFF54A45"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -937,26 +964,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1484,15 +1508,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
-  <cols>
-    <col min="1" max="1" width="33.1818181818182" customWidth="1"/>
-    <col min="2" max="2" width="47.8181818181818" customWidth="1"/>
-    <col min="3" max="3" width="255.636363636364" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:T43"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1502,74 +1521,193 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="4"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -1579,65 +1717,167 @@
       <c r="C8" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="1" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>32</v>
@@ -1645,344 +1885,839 @@
       <c r="C14" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>44</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>46</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>48</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>50</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>52</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>54</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>56</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>58</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>60</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="C31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>68</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>70</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>72</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>74</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>76</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+    </row>
+    <row r="37" spans="1:20">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>78</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+    </row>
+    <row r="38" spans="1:20">
       <c r="A38" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>80</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+    </row>
+    <row r="39" spans="1:20">
       <c r="A39" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>82</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>81</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="A42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+      <c r="T43" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model deepseek --tokenizer /home/weight/DeepSeek-R1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -ep 8 --attn-dp-size 8 --tokens-per-prediction 2 --swap-space 40 --tool-call-parser deepseek_v3" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C3" r:id="rId1" display="docker run -it --rm --privileged --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model deepseek --tokenizer /home/weight/DeepSeek-R1-0528/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.99 --prometheus-port 28880 --use-group-gemm -ep 8 --split-embedding --tokens-per-prediction 2 --swap-space 40 --tool-call-parser deepseek_v3" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C4" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model DeepSeek-V3-0324 --tokenizer /home/weight/DeepSeek-V3-0324 -ep 8 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 4096 --reset-max-seq-len 4096 --gpu-memory-utilization 0.98 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C5" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-235B-A22B --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B -ep 8 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C6" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-235B-A22B-FP8 --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B-FP8 -ep 4 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C7" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-32B --tokenizer /home/weight/Qwen3/Qwen3-32B -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C8" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-32B-FP8 --tokenizer /home/weight/Qwen3/Qwen/Qwen3-32B-FP8 -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C9" r:id="rId2" display="docker run -it --rm --privileged --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model deepseek --tokenizer /home/weight/DeepSeek-R1-AWQ/ --tensor-parallel-size 8 --port 2888 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.98 --platform-type nvidia --use-prefix-cache --use-marlin --use-marlin-wna16 --weight-dtype=FP16 --swap-space 40 --tool-call-parser deepseek_v3" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C12" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-14B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-14B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C13" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C14" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C15" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-8B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-8B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C16" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C17" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C18" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-8B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-8B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C19" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C20" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C21" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct --tokenizer /home/weight/Qwen2.5-0.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C22" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct --tokenizer /home/weight/Qwen2.5-1.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C23" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct --tokenizer /home/weight/Qwen2.5-3B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C24" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct --tokenizer /home/weight/Qwen2.5-7B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C25" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct --tokenizer /home/weight/Qwen2.5-14B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C26" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C27" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C28" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C29" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight -e &quot;CUDA_VISIBLE_DEVICES=4,5,6,7&quot; docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28877 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 4321 --prometheus-port 8007 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C30" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/QwQ-32B -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C31" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/QwQ-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C32" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-0.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C33" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-1.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C34" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-3B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C35" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-7B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C36" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-14B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C37" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-32B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C38" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C39" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C40" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B-AWQ --tokenizer /home/weight/QwQ-32B-AWQ -tp 1 --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
-    <hyperlink ref="C41" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4 --model Qwen3-30B-A3B-Instruct-2507 --tokenizer /home/weight/qwen/Qwen3-30B-A3B-Instruct-2507 -ep 2 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.1.2.rc4"/>
+    <hyperlink ref="C2" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-R1 --tokenizer /home/weight/DeepSeek-R1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --tokens-per-prediction 2 --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/nvidia_test_suite/latest/model_list.xlsx
+++ b/nvidia_test_suite/latest/model_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17230"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="NVIDIA" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
   <si>
     <t>模型名称</t>
   </si>
@@ -56,9 +56,6 @@
     <t>DeepSeek-R1-0528</t>
   </si>
   <si>
-    <t>H20 (96G) 长上下文</t>
-  </si>
-  <si>
     <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-R1-0528 --tokenizer /home/weight/DeepSeek-R1-0528/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.99 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --split-embedding --tokens-per-prediction 2 --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
@@ -164,10 +161,7 @@
     <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
-    <t>Meta-Llama-3.1-70B-Instruct_L-Series</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct_L-Series --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Qwen2.5-0.5B-Instruct</t>
@@ -206,10 +200,7 @@
     <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
-    <t>Qwen2.5-32B-Instruct_L-Series</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct_L-Series --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-72B-Instruct</t>
@@ -218,10 +209,7 @@
     <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
-    <t>Qwen2.5-72B-Instruct_L-Series</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight -e "CUDA_VISIBLE_DEVICES=4,5,6,7" docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28877 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct_L-Series --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 4321 --prometheus-port 8007 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight -e "CUDA_VISIBLE_DEVICES=4,5,6,7" docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28877 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 4321 --prometheus-port 8007 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>QwQ-32B</t>
@@ -230,10 +218,7 @@
     <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/Qwen/QwQ-32B -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
-    <t>QwQ-32B_L-Series</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B_L-Series --tokenizer /home/weight/Qwen/QwQ-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/Qwen/QwQ-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-0.5B-Instruct-AWQ</t>
@@ -278,10 +263,7 @@
     <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
-    <t>Qwen2.5-72B-Instruct-AWQ_L-Series</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ_L-Series --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>QwQ-32B-AWQ</t>
@@ -1600,10 +1582,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1625,13 +1607,13 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1653,13 +1635,13 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -1681,13 +1663,13 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -1709,13 +1691,13 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1737,13 +1719,13 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1765,13 +1747,13 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1793,13 +1775,13 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -1821,13 +1803,13 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1849,13 +1831,13 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1877,13 +1859,13 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1905,13 +1887,13 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -1933,13 +1915,13 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -1961,13 +1943,13 @@
     </row>
     <row r="17" spans="1:20">
       <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1989,13 +1971,13 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -2017,13 +1999,13 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -2045,13 +2027,13 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -2073,13 +2055,13 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -2101,13 +2083,13 @@
     </row>
     <row r="22" spans="1:20">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -2129,13 +2111,13 @@
     </row>
     <row r="23" spans="1:20">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -2157,13 +2139,13 @@
     </row>
     <row r="24" spans="1:20">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -2185,13 +2167,13 @@
     </row>
     <row r="25" spans="1:20">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -2213,13 +2195,13 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -2241,13 +2223,13 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -2269,13 +2251,13 @@
     </row>
     <row r="28" spans="1:20">
       <c r="A28" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -2297,13 +2279,13 @@
     </row>
     <row r="29" spans="1:20">
       <c r="A29" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -2325,13 +2307,13 @@
     </row>
     <row r="30" spans="1:20">
       <c r="A30" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -2353,13 +2335,13 @@
     </row>
     <row r="31" spans="1:20">
       <c r="A31" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -2381,13 +2363,13 @@
     </row>
     <row r="32" spans="1:20">
       <c r="A32" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -2409,13 +2391,13 @@
     </row>
     <row r="33" spans="1:20">
       <c r="A33" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -2437,13 +2419,13 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -2465,13 +2447,13 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -2493,13 +2475,13 @@
     </row>
     <row r="36" spans="1:20">
       <c r="A36" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -2521,13 +2503,13 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2549,13 +2531,13 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -2577,13 +2559,13 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -2605,13 +2587,13 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -2633,13 +2615,13 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -2661,13 +2643,13 @@
     </row>
     <row r="42" spans="1:20">
       <c r="A42" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -2689,13 +2671,13 @@
     </row>
     <row r="43" spans="1:20">
       <c r="A43" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -2718,6 +2700,17 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-R1 --tokenizer /home/weight/DeepSeek-R1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --tokens-per-prediction 2 --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C10" r:id="rId2" display="docker run -it --rm --privileged --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ --tensor-parallel-size 8 --port 2888 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.98 --platform-type nvidia --use-prefix-cache --use-marlin --use-marlin-wna16 --weight-dtype=FP16 --swap-space 40 --tool-call-parser deepseek_v3" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C14" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C15" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C18" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C21" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C23" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct --tokenizer /home/weight/Qwen2.5-1.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C27" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C28" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C30" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight -e &quot;CUDA_VISIBLE_DEVICES=4,5,6,7&quot; docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28877 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 4321 --prometheus-port 8007 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C32" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/Qwen/QwQ-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
+    <hyperlink ref="C40" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/nvidia_test_suite/latest/model_list.xlsx
+++ b/nvidia_test_suite/latest/model_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17230"/>
   </bookViews>
   <sheets>
     <sheet name="NVIDIA" sheetId="1" r:id="rId1"/>
@@ -44,49 +44,49 @@
     <t>H20 (96G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-R1 --tokenizer /home/weight/DeepSeek-R1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --tokens-per-prediction 2 --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --model DeepSeek-R1 --tokenizer /home/weight/DeepSeek-R1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --tokens-per-prediction 2 --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>DeepSeek-V3.1</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-V3.1 --tokenizer /home/weight/DeepSeek-V3.1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --tokens-per-prediction 2 --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --model DeepSeek-V3.1 --tokenizer /home/weight/DeepSeek-V3.1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --tokens-per-prediction 2 --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>DeepSeek-R1-0528</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-R1-0528 --tokenizer /home/weight/DeepSeek-R1-0528/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.99 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --split-embedding --tokens-per-prediction 2 --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --model DeepSeek-R1-0528 --tokenizer /home/weight/DeepSeek-R1-0528/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --split-embedding --tokens-per-prediction 2 --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>DeepSeek-V3-0324</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-V3-0324 --tokenizer /home/weight/DeepSeek-V3-0324 -tp 8 -ep 8 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --reset-max-seq-len 4096 --gpu-memory-utilization 0.98 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --model DeepSeek-V3-0324 --tokenizer /home/weight/DeepSeek-V3-0324 -tp 8 -ep 8 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --reset-max-seq-len 4096 --gpu-memory-utilization 0.98 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>Qwen3-235B-A22B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-235B-A22B --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B -tp 8 -ep 8 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --model Qwen3-235B-A22B --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B -tp 8 -ep 8 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-235B-A22B-FP8</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-235B-A22B-FP8 --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B-FP8 -tp 4 -ep 4 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --model Qwen3-235B-A22B-FP8 --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B-FP8 -tp 4 -ep 4 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-32B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-32B --tokenizer /home/weight/Qwen3/Qwen3-32B -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --model Qwen3-32B --tokenizer /home/weight/Qwen3/Qwen3-32B -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-32B-FP8</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-32B-FP8 --tokenizer /home/weight/Qwen3/Qwen3-32B-FP8 -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --split-embedding --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --model Qwen3-32B-FP8 --tokenizer /home/weight/Qwen3/Qwen3-32B-FP8 -tp 1 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --split-embedding --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>DeepSeek-R1-AWQ</t>
@@ -95,7 +95,7 @@
     <t>H100 (80G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ --tensor-parallel-size 8 --port 2888 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.98 --platform-type nvidia --use-prefix-cache --use-marlin --use-marlin-wna16 --weight-dtype=FP16 --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --rm --privileged --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ --tensor-parallel-size 8 --port 2888 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.98 --platform-type nvidia --use-prefix-cache --use-marlin --use-marlin-wna16 --weight-dtype=FP16 --swap-space 40 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-1.5B</t>
@@ -104,19 +104,19 @@
     <t>H100/A100 (80G)、L40s/L20 (48G)、H20 (96G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-1.5B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-1.5B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-1.5B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-1.5B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-7B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-7B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-7B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-7B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-7B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-14B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-14B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-14B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-14B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-14B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Qwen-32B</t>
@@ -125,163 +125,163 @@
     <t>H100/A100 (80G)、H20 (96G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>L40s/L20 (48G)</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Llama-8B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-8B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-8B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-8B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-8B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>DeepSeek-R1-Distill-Llama-70B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Meta-Llama-3.1-8B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-8B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-8B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-8B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-8B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Meta-Llama-3.1-70B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json</t>
   </si>
   <si>
     <t>Qwen2.5-0.5B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct --tokenizer /home/weight/Qwen2.5-0.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct --tokenizer /home/weight/Qwen2.5-0.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-1.5B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct --tokenizer /home/weight/Qwen2.5-1.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct --tokenizer /home/weight/Qwen2.5-1.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-3B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct --tokenizer /home/weight/Qwen2.5-3B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct --tokenizer /home/weight/Qwen2.5-3B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-7B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct --tokenizer /home/weight/Qwen2.5-7B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct --tokenizer /home/weight/Qwen2.5-7B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-14B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct --tokenizer /home/weight/Qwen2.5-14B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct --tokenizer /home/weight/Qwen2.5-14B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-32B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-72B-Instruct</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight -e "CUDA_VISIBLE_DEVICES=4,5,6,7" docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28877 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 4321 --prometheus-port 8007 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight -e "CUDA_VISIBLE_DEVICES=4,5,6,7" docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28877 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 4321 --prometheus-port 8007 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>QwQ-32B</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/Qwen/QwQ-32B -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/Qwen/QwQ-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/Qwen/QwQ-32B -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/Qwen/QwQ-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-0.5B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-0.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-0.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-0.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-1.5B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-1.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-1.5B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-3B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-3B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-3B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-3B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-7B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-7B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-7B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-7B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-14B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-14B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-14B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-14B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-32B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-32B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-32B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen2.5-72B-Instruct-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
-  </si>
-  <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 1 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+  </si>
+  <si>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>QwQ-32B-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B-AWQ --tokenizer /home/weight/Qwen/QwQ-32B-AWQ -tp 1 --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B-AWQ --tokenizer /home/weight/Qwen/QwQ-32B-AWQ -tp 1 --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-30B-A3B-Instruct-2507</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model Qwen3-30B-A3B-Instruct-2507 --tokenizer /home/weight/qwen/Qwen3-30B-A3B-Instruct-2507 -tp 2 -ep 2 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --model Qwen3-30B-A3B-Instruct-2507 --tokenizer /home/weight/qwen/Qwen3-30B-A3B-Instruct-2507 -tp 2 -ep 2 --port 28881 --platform-type nvidia --use-prefix-cache --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --swap-space 40 --tool-call-parser hermes</t>
   </si>
   <si>
     <t>Qwen3-32B-AWQ</t>
   </si>
   <si>
-    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen3-32B-AWQ --tokenizer /home/weight/Qwen/Qwen3-32B-AWQ -tp 1 --weight-dtype=FP16 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
+    <t>docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc5 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen3-32B-AWQ --tokenizer /home/weight/Qwen/Qwen3-32B-AWQ -tp 1 --weight-dtype=FP16 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes</t>
   </si>
 </sst>
 </file>
@@ -1492,6 +1492,11 @@
   <sheetPr/>
   <dimension ref="A1:T43"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="33.1818181818182" customWidth="1"/>
+    <col min="2" max="2" width="47.8181818181818" customWidth="1"/>
+    <col min="3" max="3" width="255.636363636364" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
@@ -2698,20 +2703,6 @@
       <c r="T43" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --model DeepSeek-R1 --tokenizer /home/weight/DeepSeek-R1/ --port 28881 --platform-type nvidia --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 512 --master-port 28882 --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.98 --prometheus-port 28880 --use-group-gemm -tp 8 -ep 8 --tokens-per-prediction 2 --use-prefix-cache --swap-space 40 --tool-call-parser deepseek_v3" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C10" r:id="rId2" display="docker run -it --rm --privileged --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ --tensor-parallel-size 8 --port 2888 --max-num-batched-tokens 2048 --gpu-memory-utilization 0.98 --platform-type nvidia --use-prefix-cache --use-marlin --use-marlin-wna16 --weight-dtype=FP16 --swap-space 40 --tool-call-parser deepseek_v3" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C14" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C15" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C18" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C21" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 8 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser llama3_json" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C23" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-1.5B-Instruct --tokenizer /home/weight/Qwen2.5-1.5B-Instruct -tp 1 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C27" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 2 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C28" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-32B-Instruct --tokenizer /home/weight/Qwen2.5-32B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C30" r:id="rId1" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight -e &quot;CUDA_VISIBLE_DEVICES=4,5,6,7&quot; docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28877 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct --tokenizer /home/weight/Qwen2.5-72B-Instruct -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 4321 --prometheus-port 8007 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com:80/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C32" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model QwQ-32B --tokenizer /home/weight/Qwen/QwQ-32B -tp 4 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-    <hyperlink ref="C40" r:id="rId2" display="docker run -it --rm --privileged --name siginfer_serving --network=host --pid=host --gpus all --ipc=host -v /home/weight:/home/weight docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3 --schedule-policy DynamicSplitFuseV2 --master-port 28882 --nnodes 1 --node-rank 0 --model Qwen2.5-72B-Instruct-AWQ --tokenizer /home/weight/Qwen2.5-72B-Instruct-AWQ -tp 2 --disable-turbomind --use-marlin --weight-dtype=FP16 --max-num-batched-tokens 8192 --gpu-memory-utilization 0.9 --port 8000 --prometheus-port 8001 --platform-type nvidia --use-prefix-cache --swap-space 40 --tool-call-parser hermes" tooltip="http://docker.xcoresigma.com/docker/siginfer-x86_64-nvidia:v1.2.rc3"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
